--- a/resources/data-imports/Monsters/weekly-monsters-hell.xlsx
+++ b/resources/data-imports/Monsters/weekly-monsters-hell.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -404,34 +404,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -577,7 +577,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.71"/>
@@ -842,7 +842,7 @@
         <v>0.011532755794672</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>648419054.472</v>
+        <v>8000000</v>
       </c>
       <c r="X2" s="1" t="n">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>0.0148030301588324</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>738411838.20406</v>
+        <v>9735603</v>
       </c>
       <c r="X3" s="1" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
         <v>0.0190006366027915</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>840894540.404725</v>
+        <v>11847745</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0.0243885331204255</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>957600611.878416</v>
+        <v>14418118</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>0</v>
@@ -1342,7 +1342,7 @@
         <v>0.0313042431261858</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>1090504085.5998</v>
+        <v>17546133</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0.0401809995240196</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>1241852966.63202</v>
+        <v>21352773</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0.0515748844730486</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>1414207256.16495</v>
+        <v>25985265</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0.0661996650137642</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1610482252.83357</v>
+        <v>31622777</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0.0849715068237272</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>1833997863.73983</v>
+        <v>38483350</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>0.109066367184691</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2088534759.25256</v>
+        <v>46832326</v>
       </c>
       <c r="X11" s="1" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0.13999366252905</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>2378398321.4197</v>
+        <v>56992615</v>
       </c>
       <c r="X12" s="1" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>0.179690825450438</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>2708491467.6529</v>
+        <v>69357183</v>
       </c>
       <c r="X13" s="1" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>0.230644674678466</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>3084397581.46551</v>
+        <v>84404248</v>
       </c>
       <c r="X14" s="1" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
         <v>0.29604720120899</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>3512474953.00194</v>
+        <v>102715779</v>
       </c>
       <c r="X15" s="1" t="n">
         <v>0</v>
@@ -2550,7 +2550,7 @@
         <v>0.379995529772616</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>3999964326.77917</v>
+        <v>125000004</v>
       </c>
       <c r="X16" s="1" t="n">
         <v>0</v>
